--- a/MainTop/11.05.2026 Макс ВБ/p3.xlsx
+++ b/MainTop/11.05.2026 Макс ВБ/p3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,40 +436,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Среднее количество заказов в день, шт</t>
+          <t>Num_Copies</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Остатки «Склад WB», шт</t>
+          <t>Тип упорядочить</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Остатки «Свой склад», шт</t>
+          <t>Имя папки</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>дней</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Num_Copies</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Тип упорядочить</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Имя папки</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Остаток</t>
         </is>
@@ -478,71 +458,208 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка очки с краской розовой</t>
+          <t>Термонаклейка Котенок выглядывает из стены</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>6_а4_настройки_60</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>11.05.2026 Макс ВБ</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Термонаклейка Тигр розовый крупный план</t>
+          <t>Термонаклейка Май Литл Пони радуга</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6_а4_настройки_60</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>11.05.2026 Макс ВБ</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>-14.3</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Термонаклейка Мишка моряк</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Термонаклейка Принцессы дисней</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Термонаклейка Черепашки Ниндзя надпись снизу</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Термонаклейка Единорог и балерина</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Термонаклейка Эльза холодное сердце</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Термонаклейка Единорог корона и надпись внизу</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Термобирки белые 30шт</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3_термобирки</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11.05.2026 Макс ВБ</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
